--- a/docs/downloads/20260924_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20260924_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,10 @@
     <col width="9" customWidth="1" min="34" max="34"/>
     <col width="9" customWidth="1" min="35" max="35"/>
     <col width="9" customWidth="1" min="36" max="36"/>
-    <col width="42" customWidth="1" min="37" max="37"/>
+    <col width="9" customWidth="1" min="37" max="37"/>
+    <col width="9" customWidth="1" min="38" max="38"/>
+    <col width="9" customWidth="1" min="39" max="39"/>
+    <col width="42" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -573,8 +576,11 @@
       <c r="AE3" s="3" t="n">
         <v>46276</v>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AH3" s="3" t="n">
         <v>46283</v>
+      </c>
+      <c r="AK3" s="4" t="n">
+        <v>46290</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -746,22 +752,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="AH4" s="6" t="inlineStr">
+      <c r="AH4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AI4" s="6" t="inlineStr">
+      <c r="AI4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AJ4" s="6" t="inlineStr">
+      <c r="AJ4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="AK4" s="5" t="inlineStr">
+      <c r="AK4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AL4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AM4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AN4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -890,18 +911,29 @@
         <f>AF5/$D$5</f>
         <v/>
       </c>
-      <c r="AH5" s="12">
+      <c r="AH5" s="10">
         <f>AI5-AF5</f>
         <v/>
       </c>
-      <c r="AI5" s="12" t="n">
+      <c r="AI5" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="AJ5" s="13">
+      <c r="AJ5" s="11">
         <f>AI5/$D$5</f>
         <v/>
       </c>
-      <c r="AK5" s="8" t="inlineStr">
+      <c r="AK5" s="12">
+        <f>AL5-AI5</f>
+        <v/>
+      </c>
+      <c r="AL5" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="AM5" s="13">
+        <f>AL5/$D$5</f>
+        <v/>
+      </c>
+      <c r="AN5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -1030,18 +1062,29 @@
         <f>AF6/$D$6</f>
         <v/>
       </c>
-      <c r="AH6" s="12">
+      <c r="AH6" s="10">
         <f>AI6-AF6</f>
         <v/>
       </c>
-      <c r="AI6" s="12" t="n">
+      <c r="AI6" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="AJ6" s="13">
+      <c r="AJ6" s="11">
         <f>AI6/$D$6</f>
         <v/>
       </c>
-      <c r="AK6" s="8" t="inlineStr">
+      <c r="AK6" s="12">
+        <f>AL6-AI6</f>
+        <v/>
+      </c>
+      <c r="AL6" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM6" s="13">
+        <f>AL6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AN6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -1170,18 +1213,29 @@
         <f>AF7/$D$7</f>
         <v/>
       </c>
-      <c r="AH7" s="12">
+      <c r="AH7" s="10">
         <f>AI7-AF7</f>
         <v/>
       </c>
-      <c r="AI7" s="12" t="n">
+      <c r="AI7" s="10" t="n">
         <v>61</v>
       </c>
-      <c r="AJ7" s="13">
+      <c r="AJ7" s="11">
         <f>AI7/$D$7</f>
         <v/>
       </c>
-      <c r="AK7" s="8" t="inlineStr">
+      <c r="AK7" s="12">
+        <f>AL7-AI7</f>
+        <v/>
+      </c>
+      <c r="AL7" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="AM7" s="13">
+        <f>AL7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AN7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -1310,18 +1364,29 @@
         <f>AF8/$D$8</f>
         <v/>
       </c>
-      <c r="AH8" s="12">
+      <c r="AH8" s="10">
         <f>AI8-AF8</f>
         <v/>
       </c>
-      <c r="AI8" s="12" t="n">
+      <c r="AI8" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AJ8" s="11">
         <f>AI8/$D$8</f>
         <v/>
       </c>
-      <c r="AK8" s="8" t="inlineStr">
+      <c r="AK8" s="12">
+        <f>AL8-AI8</f>
+        <v/>
+      </c>
+      <c r="AL8" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM8" s="13">
+        <f>AL8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AN8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1450,18 +1515,29 @@
         <f>AF9/$D$9</f>
         <v/>
       </c>
-      <c r="AH9" s="12">
+      <c r="AH9" s="10">
         <f>AI9-AF9</f>
         <v/>
       </c>
-      <c r="AI9" s="12" t="n">
+      <c r="AI9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AJ9" s="11">
         <f>AI9/$D$9</f>
         <v/>
       </c>
-      <c r="AK9" s="8" t="inlineStr">
+      <c r="AK9" s="12">
+        <f>AL9-AI9</f>
+        <v/>
+      </c>
+      <c r="AL9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="13">
+        <f>AL9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AN9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1580,18 +1656,29 @@
         <f>AF10/$D$10</f>
         <v/>
       </c>
-      <c r="AH10" s="12">
+      <c r="AH10" s="10">
         <f>AI10-AF10</f>
         <v/>
       </c>
-      <c r="AI10" s="12" t="n">
+      <c r="AI10" s="10" t="n">
         <v>357</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AJ10" s="11">
         <f>AI10/$D$10</f>
         <v/>
       </c>
-      <c r="AK10" s="8" t="inlineStr">
+      <c r="AK10" s="12">
+        <f>AL10-AI10</f>
+        <v/>
+      </c>
+      <c r="AL10" s="12" t="n">
+        <v>359</v>
+      </c>
+      <c r="AM10" s="13">
+        <f>AL10/$D$10</f>
+        <v/>
+      </c>
+      <c r="AN10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
@@ -1678,24 +1765,36 @@
         <f>AF11/$D$11</f>
         <v/>
       </c>
-      <c r="AH11" s="12">
+      <c r="AH11" s="10">
         <f>AI11-AF11</f>
         <v/>
       </c>
-      <c r="AI11" s="12" t="n">
+      <c r="AI11" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="AJ11" s="13">
+      <c r="AJ11" s="11">
         <f>AI11/$D$11</f>
         <v/>
       </c>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="12">
+        <f>AL11-AI11</f>
+        <v/>
+      </c>
+      <c r="AL11" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="AM11" s="13">
+        <f>AL11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AN11" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="Y3:AA3"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="AB3:AD3"/>
+    <mergeCell ref="AK3:AM3"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="V3:X3"/>
